--- a/results/scraped_Cape_Town_Arts_and_Culture.xlsx
+++ b/results/scraped_Cape_Town_Arts_and_Culture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="259">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -109,6 +109,9 @@
     <t>TOP TRENDINGDANCEMOVES YOU MUST KNOW || Party Life …</t>
   </si>
   <si>
+    <t>DanceClasses in Dallas | ApexDance&amp; Performing Arts | Dallas TX</t>
+  </si>
+  <si>
     <t>Popular Dance Videos-YouTube</t>
   </si>
   <si>
@@ -121,13 +124,10 @@
     <t>DanceHits - YouTube Music</t>
   </si>
   <si>
-    <t>Dance Styles- All Dances A through Z - Dancetime.com</t>
-  </si>
-  <si>
-    <t>JUST DANCENOW</t>
-  </si>
-  <si>
-    <t>DANCE- YouTube Music</t>
+    <t>Howto Dance: Easy and Effortless Moves Anyone Can Learn</t>
+  </si>
+  <si>
+    <t>PremierDanceClasses in Dallas - Studio 22 Dallas</t>
   </si>
   <si>
     <t>YouTube Music</t>
@@ -169,82 +169,55 @@
     <t>CULTUREDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>HoustonCulturalDistricts</t>
+  </si>
+  <si>
+    <t>CultureMap Houston</t>
+  </si>
+  <si>
     <t>CULTURAL| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
+    <t>Cultural- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
     <t>CULTURALDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>Cultural- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>Home - NebraskaCulturalEndowment</t>
-  </si>
-  <si>
     <t>Cultural- definition ofculturalby The Free Dictionary</t>
   </si>
   <si>
-    <t>Culture| Definition, Characteristics, Examples, Types, Tradition ...</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Eye Color: Truth Behind His Striking B…</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Height, Weight, Age, Body Statistics</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Eye ColorWhatColorphotos</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Eye Color| Deciphering the Enigma</t>
-  </si>
-  <si>
-    <t>WhatcolorareArnold Schwarzenegger'seyes? - Answers</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger-Wikipedia</t>
-  </si>
-  <si>
-    <t>What Is Arnold Schwarzenegger Eye Color: Over 69,699</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Eyes Color- Pinterest</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger- Bio, Facts, Wiki, Net Worth, Age, Height ...</t>
-  </si>
-  <si>
-    <t>Arnold Schwarzenegger Eye Color| The Enigma of HisEye Color</t>
+    <t>MSDN</t>
   </si>
   <si>
     <t>Choir-Wikipedia</t>
   </si>
   <si>
-    <t>Choir- Pearland High School</t>
-  </si>
-  <si>
     <t>Choir| Definition, History, &amp; Facts | Britannica</t>
   </si>
   <si>
     <t>Choir Game- Play on Lagged.com</t>
   </si>
   <si>
+    <t>CHOIRDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
     <t>CHOIR| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>CHOIRDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Home | Pearland High SchoolChoir</t>
-  </si>
-  <si>
-    <t>Choir</t>
+    <t>Indianapolis SymphonicChoir</t>
+  </si>
+  <si>
+    <t>The Avon High School Choirs is one of the premier vocal arts ...</t>
+  </si>
+  <si>
+    <t>Home | AvonChoir</t>
   </si>
   <si>
     <t>Choir (music) - Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>Encore — EncoreChoir</t>
+    <t>Choir️ Play Now for Free | RocketGames</t>
   </si>
   <si>
     <t>Youth(TV Series 2026– ) - IMDb</t>
@@ -256,27 +229,27 @@
     <t>Youth| Official Trailer | HBO Max - YouTube</t>
   </si>
   <si>
+    <t>'Youth': Premiere Date, Trailer, Cast, Plot, and More Details</t>
+  </si>
+  <si>
     <t>Youth(2026) - IMDb</t>
   </si>
   <si>
+    <t>Youth(TV series) - Wikipedia</t>
+  </si>
+  <si>
     <t>YOUTHDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>'Youth': Premiere Date, Trailer, Cast, Plot, and More Details</t>
-  </si>
-  <si>
-    <t>Youth(TV series) - Wikipedia</t>
+    <t>'Youth' Sharon Horgan HBO Review: Stream It Or Skip It? - Decider</t>
+  </si>
+  <si>
+    <t>'Youth' Season 2: Cast, Premiere Date, Plot, and More Details</t>
   </si>
   <si>
     <t>Home |Youth.gov</t>
   </si>
   <si>
-    <t>YouthSeason 1 Trailer - YouTube</t>
-  </si>
-  <si>
-    <t>YOUTH| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>Craft— Productivity App for Notes, Tasks, and Docs</t>
   </si>
   <si>
@@ -307,85 +280,127 @@
     <t>Download Minecraft Java &amp; Bedrock Edition | Minecraft</t>
   </si>
   <si>
-    <t>Google Calendar - Easier Time Management, Appointments</t>
-  </si>
-  <si>
-    <t>timeanddate.com</t>
-  </si>
-  <si>
-    <t>Today'sDateandTime-Current Date,Time&amp; More</t>
-  </si>
-  <si>
-    <t>Today's Date-CalendarDate.com</t>
-  </si>
-  <si>
-    <t>What Is Today'sDate? — LiveDate,Time&amp; Week Number ...</t>
-  </si>
-  <si>
-    <t>CURRENT_DATE(Transact-SQL) - SQL Server | Microsoft Learn</t>
-  </si>
-  <si>
-    <t>Today’sDate—Current Date,Time&amp;DateFormats</t>
-  </si>
-  <si>
-    <t>Time.is- exacttime, anytimezone</t>
-  </si>
-  <si>
-    <t>ExactCurrent DateandTime| World Clock | CurrentDateTime</t>
-  </si>
-  <si>
-    <t>Today'sDateandTime– Live World Clock, Calendar &amp;TimeZone Tools</t>
-  </si>
-  <si>
-    <t>The World Clock — Worldwide-timeanddate.com</t>
-  </si>
-  <si>
-    <t>YouTube-YouTube</t>
-  </si>
-  <si>
-    <t>AboutYouTube-YouTube</t>
-  </si>
-  <si>
-    <t>YouTube-Wikipedia</t>
-  </si>
-  <si>
-    <t>OfficialYouTubeBlog for LatestYouTubeNews &amp; Insights</t>
-  </si>
-  <si>
-    <t>YouTube(YouTubechannel) -Wikipedia</t>
-  </si>
-  <si>
-    <t>YouTube- Google Accounts</t>
-  </si>
-  <si>
-    <t>YouTube| History, Founders, Purchase, Google, Music, Videos,</t>
-  </si>
-  <si>
-    <t>YouTube- Apps onGoogle Play</t>
-  </si>
-  <si>
-    <t>Fruit Riot - Product Request Form</t>
-  </si>
-  <si>
-    <t>Fruit Riot - Product Request Form v2 - Compressed</t>
-  </si>
-  <si>
-    <t>fruitriot.co</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <t>Connecting People Through Everyday Moments | About Instagram</t>
-  </si>
-  <si>
-    <t>About Instagram: Features, Safety, Community &amp; More</t>
-  </si>
-  <si>
-    <t>Help Center</t>
-  </si>
-  <si>
-    <t>AI Studio</t>
+    <t>Disk Management in Windows|MicrosoftSupport</t>
+  </si>
+  <si>
+    <t>5 Ways to OpenDisk ManagementonWindows10 or 11</t>
+  </si>
+  <si>
+    <t>Overview ofDisk Management| Microsoft Learn</t>
+  </si>
+  <si>
+    <t>OpenDisk Management in Windows: Quick Guide - Lifewire</t>
+  </si>
+  <si>
+    <t>How to Open &amp; UseDisk Management in Windows11?</t>
+  </si>
+  <si>
+    <t>The Ultimate Guide toWindows Disk ManagementUtility</t>
+  </si>
+  <si>
+    <t>7 Easy Ways to OpenDisk Management in Windows10 and 11</t>
+  </si>
+  <si>
+    <t>How to OpenDisk Management in Windows11 and 10 (6 Ways)</t>
+  </si>
+  <si>
+    <t>How to Open Disk Management in Windows 11- All Things How</t>
+  </si>
+  <si>
+    <t>Manage disks | Microsoft Learn</t>
+  </si>
+  <si>
+    <t>Can YouWorkWhileon Disability?2026 SSDIRules &amp; SGA Limits</t>
+  </si>
+  <si>
+    <t>Social Security Disability Income Limits for2026(WhatYou Can Earn...</t>
+  </si>
+  <si>
+    <t>SSDIEarningsLimit 2026| Key Legal Rules Explained</t>
+  </si>
+  <si>
+    <t>SSDIIncome Limits2026Married: How MuchYou Can Earn</t>
+  </si>
+  <si>
+    <t>Working Part-Timeon SSDI: Income Limits and Rules (2026)</t>
+  </si>
+  <si>
+    <t>Can YouWorkWhile on SSDI?2026Rules | Peña &amp; Bromberg</t>
+  </si>
+  <si>
+    <t>SSDIEarnings Limits for2026: WhatYou Can EarnWithout Losing ...</t>
+  </si>
+  <si>
+    <t>SSDIIncome Limits2026: $1,690 SGA &amp; Trial Work Rules</t>
+  </si>
+  <si>
+    <t>How MuchCanIEarnand Still GetSSDI in 2026?</t>
+  </si>
+  <si>
+    <t>Social Security Disability Benefits Pay Chart (2026)</t>
+  </si>
+  <si>
+    <t>Tour -5 Seconds of SummerOfficial Store</t>
+  </si>
+  <si>
+    <t>5 Seconds of Summer- 2026 Tour Dates &amp; Concert Schedule -Live Nation</t>
+  </si>
+  <si>
+    <t>5 Seconds of SummerTour 2026 – Dates, Setlist &amp; Tickets</t>
+  </si>
+  <si>
+    <t>5 Seconds of SummerOfficialStore-5 Seconds of SummerOfficialStore</t>
+  </si>
+  <si>
+    <t>5 SECONDS OF SUMMERANNOUNCE ‘EVERYONE’S A STAR!’ …</t>
+  </si>
+  <si>
+    <t>5 Seconds of Summer- Climate Pledge Arena</t>
+  </si>
+  <si>
+    <t>5sosTour Dates and Locations - Facebook</t>
+  </si>
+  <si>
+    <t>Ticketmaster Blog | Music, Sports, Theater, Family &amp; Fan Insights</t>
+  </si>
+  <si>
+    <t>Find tickets for '5sos' atTicketmaster.com</t>
+  </si>
+  <si>
+    <t>Everyone's a Star! World Tour - Wikipedia</t>
+  </si>
+  <si>
+    <t>PetaPixel | Photography and Camera News</t>
+  </si>
+  <si>
+    <t>Reviews - PetaPixel</t>
+  </si>
+  <si>
+    <t>The FPV Drone Footage From Ukraine Is Unprecedented - PetaPixel</t>
+  </si>
+  <si>
+    <t>Sony RX10 V Review: Sometimes the Best Still Isn’t Good ... - PetaPixel</t>
+  </si>
+  <si>
+    <t>Caira Camera Review: A Real Head Scratcher - PetaPixel</t>
+  </si>
+  <si>
+    <t>News - PetaPixel</t>
+  </si>
+  <si>
+    <t>The Current Chapter of Pentax DSLRs Is Officially Over - PetaPixel</t>
+  </si>
+  <si>
+    <t>The 29 Finalists for Astronomy Photographer of the Year - PetaPixel</t>
+  </si>
+  <si>
+    <t>OM System PEN Review: Too Familiar But Oh-So-Pretty - PetaPixel</t>
+  </si>
+  <si>
+    <t>Tickets for Fujifilm’s New York Fujikina Event Cost $10 ... - PetaPixel</t>
+  </si>
+  <si>
+    <t>Loka Yoga Studio</t>
   </si>
   <si>
     <t>Arts &amp; Culture</t>
@@ -394,352 +409,367 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ffc7632285bcbb1ad54c234efc520889717a30f72b8c4fb6f6192e5de3c9b2cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cuZGV2aWFudGFydC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39ffc08593e8754778d43b48ea0b2099fa3a67b9004e1c95062137ab24e7b3d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXJ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22dc21841b17389689156fca59f4297d53f2a432a0e6a322dabec996ab9ac205JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly9za2V0Y2guaW8vc2tldGNocGFkLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acc4afb3fd399db9f90764c8fee9fcbe50fc19c5c60c926b93254aa289665990JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cuYXJ0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=726e4c8b00f3f5d306a79013c9f776a0fab0b7db31e0dcab093fd9913c46f442JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly9rbGVraS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2ebf616ada40b46eafe078fca0507d48b60dd68a1eaec5a1bf228003fd0f03bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly9hcnRzYW5kY3VsdHVyZS5nb29nbGUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4de4a776988a284ac522dc0cf231bef7e6a040d2a5e1e36b0cef0f93a73fed16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L3Zpc3VhbC1hcnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e92d06f0edb203599ccda57c97af09c4d19d3174a7bf4664bd99bd3a5ade7fc7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS9pZGVhcy9hcnQvOTYxMjM4NTU5NjU2Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8989855a09164c426f22e4c4235b2d2612e316e67e6e0d3d891f710093ab63cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cubmdhLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ae34e308a8f48b7dec48e1f16f7acc43ab01e967183b7de5953a347095e948eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cac87fc-7ff5-6f23-296b-901e7eee6e60&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c16f4ff9d4ce06eb49fe22234dad7e6950aac4e4369bb5eb8573deac5e98540JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af831ce5cc65163b7e5947f152b9a3c98ede6c8b2bd113a15213c9a34cf022dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHliZWVyLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=15a6dbcbef2a30bd853c042bc1bc4577ce4c7d7fd4dd1a7856153bdedf999318JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f9b70a18a3578c8de0e0b42db27495df7fe45aaef3d30b36f8bfe79e24b47f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly93d3cuY2Z0ZXhhcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca7ac7b79ca8bd42c8fb555f856bdbdb148a7bd1fa3d29193d78d19155a19997JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly93d3cuZGFsbGFzY29sbGVnZS5lZHUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f475bb6daaf77d9f9d2b19747501f425ce18b1412e462b05ab60ad5723e97d9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd83e4f6689b6c42b4bcafd761b335d191a464c6d69f31021c50e84aef7a1646JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f07c2684cb4b668add5ea0f7328ad92f1bbf4344c07f72d322bd81e2e2e40140JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec4f180fc69fa2ca839f024696acf16dcd54dcae1bdeba5fdbf0e6bc98257fa7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlpbXBhY3QuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed1ed65e18fb239122cb718fa5a65a00db9ec6a01233c8a68dca9427a5e48ae9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19a24ccf-7732-6368-3665-5b2d762d6232&amp;u=a1aHR0cHM6Ly9zb2NpYWx3b3JrbWV0aG9kcy5jb20vd2hhdC1pcy1jb21tdW5pdHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8ad5c3516bdbd9d1f9fb6c9660f6cdb4a075f56b3d66fa944c8d7e3210c9aa6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGFuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9342f5c0378e3075ad46d8c92200e73cebcfc36be98e27cd8bd40d59e9307b8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2RhbmNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd40992299a987acae1a3f2dccb1078c360526b324fc8fb2f7d8e466a3300afdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1ERnREcEZpVUdKRQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acf422b229c3ba695d7b6dbad5fb25e01dd4b11951465103ceaa226658f621ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vcGxheWxpc3Q_bGlzdD1QTGYtYXNKMGlrR011UWxidjBQdEVWZmxCWHFjdUpqMENh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8052f99c185f7aa08ed669d76302d5810c2a1cdc9e0c7c60ce8240c0f10fa228JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly93d3cudGlrdG9rLmNvbS90YWcvZGFuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52bf76fffdaeda719ec404931b080e2d01798504040c8e94cbecae4b0d80b990JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9kYW5jZV9zdHlsZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9b0dea5f0faf237314cf7e68000652438377709201c71438eecd51277b02d66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS9zZWFyY2g_cT1EYW5jZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a38d5360b150bc3957a56c2ee23747466c02e320ee5dc7d72f848256a58c26dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly93d3cuZGFuY2V0aW1lLmNvbS9kYW5jZS1zdHlsZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2aa812da61cfc11c8a4663e61fe29f93f6aba4c335e008875871b14e4b820357JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly9qdXN0ZGFuY2Vub3cuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3df47ba303538c8909da5b054c8131730ab4441ca75c9c5603e08b969505b281JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38eaa804-34a1-6628-14d3-bfe6353a6704&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS9wbGF5bGlzdD9saXN0PVBMQm52d3RoWm1VY3IxaklCMzQ2d1FWRnBwZVFHYmZ0Y1I&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c2df17011a63dde9fa04af47afdbadd22cb3df8ce4db433943f9301b6cdee9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cc12e9d86094b884062c251e5dab5b4acc347be1632203de9fdb983aa1e72c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTXVzaWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ee2cd52d5b86c0554a67d415ea74269cf6838dde1894d4919b37afee9a1cd9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2FwcGxlLW11c2ljLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adb76a164ceed8c31d4cf8dc629a8ecdfe0a92bbc4ded748638acf9d55e64207JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly9tdXNpYy5hcHBsZS5jb20vdXMvbmV3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f0e766481aa5b4fde7fa2f0b3b1a85e7eccbea0df3c50da3a35ba07a8a1c17aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQy05LWt5VFc4WmtaTkRIUUo2Rmdwd1E&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39b67610ef4eb44736782ccfe90fef22e5bcc08b541c6ee60d307a6f3387890cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly9vcGVuLnNwb3RpZnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c571bd12f17affdacea3482a00a1b5d7fa53a82072b945abd52a90f403ce0edcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vZmVlZC95b3V0dWJlbXVzaWM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf0413f78bc91fb468c2230fa0f7bba92bb98c39ea0bed624beea18cd903eeb4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly93d3cubnByLm9yZy9tdXNpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c97183941ebecd0d759fe45b348d718fd6895ae7b706b175a9e67490ea24068JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13af5d7a-3974-6396-31ae-4a9838cf628e&amp;u=a1aHR0cHM6Ly9hdWRpby5jb20vZ2VucmVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6913e0b39ac7b2133b5d2bf9ed44f68ac5e732cef1c5fd8bd7f8a4e8d1425a0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2N1bHR1cmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d506d56466fe3cc1ff4526ebccf0662779a25bac9de053b23af44c02632b085aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3VsdHVyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c498b80e590bc7e0a4118b6afaefb68d49f9bdeb34b491ae04e78b7d1573c801JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2N1bHR1cmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c47a846705d50c2043903ccf6ad483427e303a3a4249c9b8687648ad69cd6cfcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2N1bHR1cmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1f770f5c69c07fb6b80210ff48d565087d198b8e43f829fc1bd9c5ac438c7ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2N1bHR1cmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8db0a8e9522822771d109c88dc05a83b959dea6d406e47c7d45a1640ce5dc542JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2N1bHR1cmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60a1e6e8a105cd3d1518ba8927a818e787978a9390dd6846779c8fc5fd58f2e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jdWx0dXJhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=455963f5ffea1788b25d1a163edfa92f96c721190166dfbd54775a6bb80cc4efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly9uZWJyYXNrYWN1bHR1cmFsZW5kb3dtZW50Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1801e745dfdf3be48d0de9bcdd7622699e7c16d0c00f9729233181e5dc80b648JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL0N1bHR1cmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f84c1ed37fcaa8059d733d0d4565e3d27de14c26b99259b86fc990b48fd5e2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=365ce20f-3841-648d-11fa-f5ed39ac652f&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvY3VsdHVyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b24bdd96921c22d5d16013e2bb662fa5e7f8edba15b4a6d4bc1eeb36889522f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly9zdGFyeGJpby5jb20vYXJub2xkLXNjaHdhcnplbmVnZ2VyLWV5ZS1jb2xvci8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46f3d4337ba72b3ec61951a21a9a6b6e7aa0b90fece12c6638054f4a774a1641JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly9oZWFsdGh5Y2VsZWIuY29tL2Fybm9sZC1zY2h3YXJ6ZW5lZ2dlci8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49caaad85af504f90c36739c394d03047dd5287476237931c0c806e82579820eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly93d3cuc2h1dHRlcnN0b2NrLmNvbS9zZWFyY2gvYXJub2xkLXNjaHdhcnplbmVnZ2VyLWV5ZS1jb2xvci13aGF0LWNvbG9yP2ltYWdlX3R5cGU9cGhvdG8mbXNvY2tpZD0wYzJmMTk1ODI2ZDI2YWFkMjUxMzBlYmEyNzNhNmJhZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0620202a631e4f0f717f262f4b0d42666aa9f9caae5d582ed14b70b3720cca5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly9sZWFrYmlvLmNvbS9hcm5vbGQtc2Nod2FyemVuZWdnZXItZXllLWNvbG9yLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa856f27f28d1d1832db3048e86e4ca476464280223d16e948c5f402c95d315aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly93d3cuYW5zd2Vycy5jb20vZ2VuZXJhbC1hcnRzLWFuZC1lbnRlcnRhaW5tZW50L1doYXRfY29sb3JfYXJlX0Fybm9sZF9TY2h3YXJ6ZW5lZ2dlciUyN3NfZXllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1384278caa038afddbfe493a17f40676a7e17f738c26a5a5aa7626ced5222e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXJub2xkX1NjaHdhcnplbmVnZ2Vy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3f5e288167cebfe01a3250fb5deb18e79fef335404d4a420b8e821ce6d389abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly93d3cuc2h1dHRlcnN0b2NrLmNvbS9zZWFyY2gvd2hhdC1pcy1hcm5vbGQtc2Nod2FyemVuZWdnZXItZXllLWNvbG9yP2ltYWdlX3R5cGU9cGhvdG8mbXNvY2tpZD0wYzJmMTk1ODI2ZDI2YWFkMjUxMzBlYmEyNzNhNmJhZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c6e50b813333486b7f7d18afee6f6d40232621996e582baf272187e232456a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS9pZGVhcy9hcm5vbGQtc2Nod2FyemVuZWdnZXItZXllcy1jb2xvci85NTQ5Mjg2NzkwNzAv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2dd95d8c518f78ae2b23ee15e4cf02d8669363235506e336e55fb9e7e17d9e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly9mYWN0bWFuZHUuY29tL2Fybm9sZC1zY2h3YXJ6ZW5lZ2dlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31fe5b699dbaaf09d0f67a0ff1a85115fef4acea095de78d26c14ca9d728eb5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c2f1958-26d2-6aad-2513-0eba273a6bae&amp;u=a1aHR0cHM6Ly93d3cubGlua2VkaW4uY29tL3Bvc3RzL3RhbWF6cmFyaXp3YW5fYXJub2xkLXNjaHdhcnplbmVnZ2VyLWV5ZS1jb2xvci10aGUtZW5pZ21hLWFjdGl2aXR5LTcxOTcxOTQ5NjkxODEyMzcyNDgtdmlGUg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ca9d4a6993a03584da4e1455ae9b849dcff09a7ace32b27eb360f15fe2574beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2hvaXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b9e465f2436802326c57debd290fe0f05dc56bf0edff336eca79a404b9a6fc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly9waHMucGVhcmxhbmRpc2Qub3JnL2ZpbmUtYXJ0cy1waHMvY2hvaXIvY2hvaXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d69be275fd67d32477db1b97c922d501faffaebddaf754656c7debc227a861dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2Nob2lyLW11c2lj&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=effab5bff530131af681812a6650d67c61db38b101c421608e3b97af53ea4f7aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly9sYWdnZWQuY29tL2VuL2cvY2hvaXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cb7eecd9cca26e101ec8cb11a7b4c311b66ef3c15d16bf311ef5d0a21aadedbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=957388ebfc83c546fe3f05eb7402fdb9f3b3095bf380b404e65f49f2c11d53eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a6484eb9b45ea13088c2a5aba8bf86879991b28312078df5e42c28ce30d86ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly93d3cucGVhcmxhbmRoaWdoc2Nob29sY2hvaXIuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97821e0ed4861c4dfdf518562bacc4b98861e526679aa0ef42803d14e43ededcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly93d3cudWlsbXVzaWMuY29tL2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad3f41639a56c539f0da018098a675bfbf2effc302d1e1c9b2b69f3d4fb128cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0Nob2lyXyhtdXNpYyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=830452ea5b83061eae48377f0015387896f5b2d1173f866926ebaddc4fa071a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f11c597-ce68-63cc-2773-d275cf866298&amp;u=a1aHR0cHM6Ly93d3cuZGhzZW5jb3JlY2hvaXIuY29tL2hvbWU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=571070abe0f9bb7c5c935e6fdc2f658837e8f9d93c33183f4a05e8a5b0bcb525JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d77072f66319fe6dc0d9511171fee957c116d449818f737d0d954ba800f7a96bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=107be7407ebbcbbfc5ce379bd34aea2632440453c09b44a1ec4657dec3012c5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd86df17993cf35daca8e663a4c7f23b3f047d113a8c3b8de06a6960e2db0cc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d65fee95875e3c4c26921b45e1f029b67d864313bb883907013a3374cd3bb3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c06315e53f660b726e56664a3a037a50233bc109e04551dd463cf5dca86d784aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d96dfeeb8bf99db03dd884541a577c9a351da98bf26e9710260123e65a70734cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b75701dd33792a69c2ce3ad534572a2d0141a4968cb1820ecc9b7d297bab19c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=681307c60c85e56eb3da91b98965e12c57cf6b6e2d3f3b4de7b0e760b04f5192JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0yeGh0Q19pV2NnWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8aaad20eb412336985db8ad0dfd036f78202247ddc19fbf85be3d854c37e8ef0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07be1771-2708-66df-29d5-0093267b6717&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e2fdbe1eae2c31921d89af357c456a40eb9c58f9e68807e70391db24a31042eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnQuZG8v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c76c2d2e75d2503d19c3cbdc2792bcec2e0d7f1c13efa6e8b1df2710117b797JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQzI5NS1Ed190RE50WlhGZUFQQVc2QXc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a51eeec8af2fa8608149352f8fb3095d8951cd986e7c96cf79cf36f2361245b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bFdJMUNIS1RmRjA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7eafb48515143a8094e2500fadb01429f125f37883f2542412636a912cce918JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DcmFmdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=476d8a31cb67150e5a296fc50b9266e43bb1ac66c16bc9686eaf10048a99f97eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnQuZG8vZG93bmxvYWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6273c36c4ea511c52a83c317f4bde6e85e4b48e0a1748c5befdd7d14bf279a7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cuZ29vZGhvdXNla2VlcGluZy5jb20vdHJhdmVsL2hvYmJpZXMtYW5kLWFjdGl2aXRpZXMvZzMyMzM2MTUxL2FkdWx0LWNyYWZ0LWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=198e13d154413159affe15385e406bbdbeb4114475384c01e06420e457f6d212JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NyYWZ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86b2f74dcb57b261541ac353465ad480dcdb12048f26273086310aea21695495JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnRzcG9ydHN3ZWFyLmNvbS9nbG9iYWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee8996a52f488570eed5b97c642414f8f861ef78a816cb9787f70cbbfc8b5be9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cudGhlc3BydWNlY3JhZnRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6c08c6386b6cccf6d16f25fc48b85bc9c808b1114aae9c8e08b2e04ed8a3c41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18f5c9c2-73df-6dbf-314f-de2072d96c45&amp;u=a1aHR0cHM6Ly93d3cubWluZWNyYWZ0Lm5ldC9lbi11cy9kb3dubG9hZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74ea18928ff94fc357a339c6d40e062d33b302c287f08b017713e87a61f1e2e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d8dca91-6c81-65fb-31d0-dd736da0640c&amp;u=a1aHR0cHM6Ly9jYWxlbmRhci5nb29nbGUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3e7d4d0a2bdad3618501c867de69c977399ae63552dd7382a2cba7726e2b237JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24509fefa678db73134dd3ee8e236e080efd34b3164b22eed063e5e353e8d36dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly90b2RheWRhdGVhbmR0aW1lLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7232a420a9ccbf8490c076448b7a03bf7c46eab49a0bc2881d70ccf6a5eb4f74JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly93d3cuY2FsZW5kYXJkYXRlLmNvbS90b2RheXMuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e69f8af878d01ca8f4b8f00dacc81313fd8488e6029d2b43fe62c7ebe8bf2385JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly90b2RheXNkYXRlYW5kdGltZS5jb20vdG9kYXkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d74085dba1a579d5685b9d02104834d4acf8a7e2adc66de0e4b8239745bbb253JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly9sZWFybi5taWNyb3NvZnQuY29tL2VuLXVzL3NxbC90LXNxbC9mdW5jdGlvbnMvY3VycmVudC1kYXRlLXRyYW5zYWN0LXNxbD92aWV3PXNxbC1zZXJ2ZXItdmVyMTc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51b51fcdb0324bad8075f481a52057493fb16881d1a5bf49781337c46fc74a0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly9nZXR0b2RheXNkYXRlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ae4e21e328e4dd93437854a1c7aa898b89c0054c8b68d1d6f53dbd653aa2535JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly90aW1lLmlzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfbec96c92346c31a985ee354cb04f8a77ac781a82df203cccbe5ba6c3a1a435JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly9jdXJyZW50ZGF0ZXRpbWUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=026e2cc1d2b80c2405b4f67547b1b09d36f4b9acf954f7600546520d7903f278JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly93d3cudG9kYXl0aW1lYW5kZGF0ZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85447cfc4022ad9d2099020be8fb80dcee39194fb3790deab6292f91e25cc6a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2da1e6cb-d70d-6b4e-0b2d-f129d64e6a42&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2sv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b50143e9b1fab199c6d585f28788bf369789c2ec2df5a62d0b82bb8d5c37f40bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20veW91dHViZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc128d20f271c67f081a972b39c79468df99456e2b4f1729b58f7bc1c668540aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9hYm91dC55b3V0dWJlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8cea5142231bf1d9e32ff79b85eaa3d4c52c7d5cbb96dc7336f0383fe13ebc37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91VHViZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9670c1b5cf840c9936e37cae666c71e46e045f46eb2c3ad0b819d541ce38221JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9ibG9nLnlvdXR1YmUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3b2e4ed82afab76ff6abcfc83aaca11858d2e2777eaf7d350b262ef065b0b6fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91VHViZV8oWW91VHViZV9jaGFubmVsKQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb8fc53aa30f527f05484d04ad991241cba8b3af2d2ae89f724f69bc91508c42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT15b3V0dWJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d9017ad4553fe553fb89c055eb62e3dbfdc8f8767ca8573cd4c30059f257258JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvWW91VHViZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a4edcfa8d3874a068f8d0b8dc362aaae5b49a6a69e59480266888c4d07dfafbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=121e903b-8341-605b-0d53-87d982e661d3&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5nb29nbGUuYW5kcm9pZC55b3V0dWJlJmhsPWVu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2e5e2854730b90d7cd11939433a0c6825c80b6d65608d8cf974c718b9a1a2eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a337a69-95b8-678f-0ba2-6d8b94146673&amp;u=a1aHR0cHM6Ly9mcnVpdHJpb3QuY28vd3AtY29udGVudC91cGxvYWRzLzIwMjMvMDkvRnJ1aXQtUmlvdC1Qcm9kdWN0LVJlcXVlc3QtRm9ybS5wZGY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdeeaeb4958e4de6804cee06ebb7458896915f31f60345cd8b4754c5579993a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a337a69-95b8-678f-0ba2-6d8b94146673&amp;u=a1aHR0cHM6Ly9mcnVpdHJpb3QuY28vd3AtY29udGVudC91cGxvYWRzLzIwMjQvMDIvRnJ1aXQtUmlvdC1Qcm9kdWN0LVJlcXVlc3QtRm9ybS12Mi1Db21wcmVzc2VkLnBkZg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=627377441c5fb02cb088caf194b77cf47565b0fad02db5a9f94e29e060d2f4f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a337a69-95b8-678f-0ba2-6d8b94146673&amp;u=a1aHR0cHM6Ly9mcnVpdHJpb3QuY28vd3AtY29udGVudC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9d4468c598c7a4396ccad23638f55173b5c5436f0019c409c4d7cbb0ee32105JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c46c0f4-19d7-6536-117e-d71618c36403&amp;u=a1aHR0cHM6Ly93d3cuaW5zdGFncmFtLmNvbS8_aGw9cHQtYnI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=393dbf29ab4d2946d3c08555d5dbd522d48be89103e4adf2b98207107b363090JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c46c0f4-19d7-6536-117e-d71618c36403&amp;u=a1aHR0cHM6Ly9hYm91dC5pbnN0YWdyYW0uY29tL2Fib3V0LXVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d61969729ab3a2187c96126e585e86fc26044eef3ab20d06e0b8a0cac0b6af05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c46c0f4-19d7-6536-117e-d71618c36403&amp;u=a1aHR0cHM6Ly9hYm91dC5pbnN0YWdyYW0uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af493ce2ea18e60034a307472b3fb5e0aa5cdba2d375d0cfc7dad18727d02ac5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c46c0f4-19d7-6536-117e-d71618c36403&amp;u=a1aHR0cHM6Ly9oZWxwLmluc3RhZ3JhbS5jb20vMTA2ODcxNzgxMzIxNjQyMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dc1c4314c216308769e05d8d51c1606074f385b932515f9af965f719253b98bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c46c0f4-19d7-6536-117e-d71618c36403&amp;u=a1aHR0cHM6Ly9haXN0dWRpby5pbnN0YWdyYW0uY29tLw&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf1d5d472eac608dbd46d4f2037741baeca2fab390fd9992bea96193c5fa4980JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cuZGV2aWFudGFydC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a82de8fcef7925c8adaf65cdab783940041f71756139d9814b36bf574ad28d2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e968d0a24d1ff7770d148692f572ec7aaf2008c379dd32384cb74552076d2a10JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly9za2V0Y2guaW8vc2tldGNocGFkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=545cfab4dbf1704987895dd577e4f00b45fa29fd45901d776f21ea74944fadc3JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cuYXJ0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=460cbdc5bfb321eaef2d87a4f6958e78f80670bc805192c9181d825a7b0393a6JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly9rbGVraS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9ce3988606e2ec7abda5fe8db92aa04ab75dfeb31f73bfcaf978e20bf301df1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly9hcnRzYW5kY3VsdHVyZS5nb29nbGUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1756ce9d698c002202d65cb0d7004388e5358aee16cc598d8b4e2c70434e4191JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L3Zpc3VhbC1hcnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52bf6af59f38d39cc2dc74e4d16a0ab152f07d0d0f37219c8b220e17525a8673JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS9pZGVhcy9hcnQvOTYxMjM4NTU5NjU2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4679a5ddf01716b6f5b739d238902ec90f8df0df7898cb3b9319f53dac1a59eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cubmdhLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5e0d9766e20abb0ad80e5dad443d8407c5424a7f8f293ba898ce9129a0cab41JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36193c65-95df-6a30-2c32-2b87942e6b1f&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f85e8462ab5cfc06d9fdd3d86c92b5c10d2b178a140c57383ceadc9f0ba05f7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da0457a22048da481d9fa3aa288339c49c2ad05a1762a384f9a584eee75583bbJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHliZWVyLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1387c06f84001e3aa676930ac5feb8c59181e0992889f86fec8ecf21ef01872JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef411183b3b7cc780bc41821613dae37a89459bdd82d6e4c5c44b099a34e69a7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly93d3cuY2Z0ZXhhcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a660c16ca0353169e25dd7c838d8dd79beb39c389ed3743d6afbc0066217fffJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly93d3cuZGFsbGFzY29sbGVnZS5lZHUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4a726514d4a40f3064b41338d13fd09ef64b4bb1ac0b7d071a88278abb54e01JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91d95758c996f1a40c1efba556d01b688a271b5c6b35a8b889cacc30567fef23JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=531e5b33841d08c358c4b090af5dd8c27983f450935b0dea7fcd618059064172JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7794ff38e130ac4640098f0dfba357807b53056ec2e6ce17ea0a588857e95590JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlpbXBhY3QuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eea4e205af7cafb709f845e8f3b8f33e3a389a1216f585edb28e8296b2494d18JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04d84192-34db-6795-13b7-567035b36636&amp;u=a1aHR0cHM6Ly9zb2NpYWx3b3JrbWV0aG9kcy5jb20vd2hhdC1pcy1jb21tdW5pdHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44b37054c0523f65631e58f7c12a9de02993a9a086308afa0a9ee89567db0403JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGFuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167eabc7056a1168c6463d6ae0fc52012e86497c7d910ee660263d3a06a029e9JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2RhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ad7fc09355906b3452c023196df0d1a1d353535bd1c55843f469fc816ae33e3JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1ERnREcEZpVUdKRQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54c0f8546a0abaa311d77a5dc2a9208af92caf52ae0afe269c618acf4f8a4596JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cuYXBleGRhbmNlY2xhc3Nlcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=468fb71d9bf29d490152d69e9538bb71422a0afd8d3c2c2f0e69da0c41b30254JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vcGxheWxpc3Q_bGlzdD1QTGYtYXNKMGlrR011UWxidjBQdEVWZmxCWHFjdUpqMENh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be0c960f6066e5f311c7bd460f2f362037d29e83a68785516c86c03dc7fb113bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cudGlrdG9rLmNvbS90YWcvZGFuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3aaa5256152371d48d4815cd1a9b4664515a7f12bea656e7299b5fece0a22dacJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9kYW5jZV9zdHlsZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b00b510e8cd87d322de006766f53f35450e397bd6bcd6fe45a152d5a9b70ae44JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS9zZWFyY2g_cT1EYW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42ba4676c7f57279ec468e955fcb6ed750e1e52417c27bfdecc8a5580effca41JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vRGFuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=598200f2f45a1ee0e32d3c8d6ffec11009573716f44274281ccbceeca45ed6c7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba207b8-6f07-6e4c-1f78-105a6eec6f3c&amp;u=a1aHR0cHM6Ly9zdHVkaW8yMmRhbGxhcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb2971bcbbd0f549e3d188fe56773637aae018f2c800e6ab38b258ba941680f0JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c246f081b465c6299821ea62d16ae0ba781de5fd025addee38798d6a40f0d5ccJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTXVzaWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac0d3637fca32d2374420f634b4c7736d7f746ff8a1cd716e0b88fdcf1b0870bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2FwcGxlLW11c2ljLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b0f86c720127aff399b52a4e2ae60a28f9bea571010809d9991d64d512e15f9JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly9tdXNpYy5hcHBsZS5jb20vdXMvbmV3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86c33bbbfbc9d878c59ba52953fc1a41442fbdeae25c851d0306654c473e75f5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQy05LWt5VFc4WmtaTkRIUUo2Rmdwd1E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb0a79d3377e00bfeaec53410f18ef0321b4249506c85e7b5f3ef5396a42568aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly9vcGVuLnNwb3RpZnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6228d678074fdb052f220844af4d7ff8e1db96143a7e1278282692cb0700fc7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vZmVlZC95b3V0dWJlbXVzaWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd585b1a9cd690a2efacbdd0b682ea6aad52a30c8d4e96e11261585ea171553eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly93d3cubnByLm9yZy9tdXNpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a51af4b896b2bebe76a00712aa599aef9f2f0597807aca257427948ccec8597JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1161a8dc-eef6-66d9-34b3-bf3eef1d672f&amp;u=a1aHR0cHM6Ly9hdWRpby5jb20vZ2VucmVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93be02a9304d88e1a1bb37b6d3c99cec891e40d24330a4d24f3287f15699e289JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2N1bHR1cmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5054c3355fb10b313941331a3d8fc79a8e1cdfc077a2e1eee19e28331d9aed89JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3VsdHVyZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f8d8f7113de6a468088af79dd193f179ef324a75336c8744b07eed680972da1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2N1bHR1cmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71a1192c00ca89707d6ecfafbf46572d60a42efcb8226bd3268aaa25f5e0ab2cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2N1bHR1cmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9deba7622d40384b4ef76529d8b2720b0362e2993861505b3bdd7cc4b489633cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly9ob3VzdG9uY3VsdHVyYWxkaXN0cmljdHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac8fdae5a4d7a0ffba378415d2ae00532009c6556d06807ef045d78f884bc31bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly9ob3VzdG9uLmN1bHR1cmVtYXAuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=105c5f4f3c663150dde250e2ddbc541f52a65e847bd907ab2cecb983784ec6efJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2N1bHR1cmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd1c1eb201f7722820c71cfbe6772f2f9f78cfbd102c3b627d65e4df1e5d5224JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jdWx0dXJhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27c3235a00143a851a5e74839a40c0e1c74137beb8904a262b0021dba83b2578JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2N1bHR1cmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e778c9fcf095b5ab7ef1f804cb97f896b477fab9d4c21b084337dc28785ea017JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39d10c89-9c9c-69f5-318b-1b6b9d1c68e7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL0N1bHR1cmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68f4b7562cd8638a59dff04e8da0e4125ae066c81473c2fe9e488b490b96fdfaJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2515ce2c-39f9-6704-3475-d9ce38e06652&amp;u=a1aHR0cHM6Ly9zb2NpYWwubXNkbi5taWNyb3NvZnQuY29tL0ZvcnVtcy9lbi1VUy9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17abf35d91dc84ba3ecefd759f6a170424301bb07035827bc737c6bf37cc1e60JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2hvaXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0697a5f5e281134d2b6458cef552711850b5649a5a3df532ffbd71926efd5118JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2Nob2lyLW11c2lj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7993f75adcb5bc69b0a69450a8d0b1af85ab961e136d1e88b2aac3f765a0018eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly9sYWdnZWQuY29tL2VuL2cvY2hvaXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e839a8e1d4670a5386a24cbda87f176302b1e4dd327e9688cc88b9a7aaa7562JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Nob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=369895a3e97fca89ac832396453e2357080db3bb87ba7dba259941be9cb3e37aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8917f7696f950468437f969c1dd8a391b844a9167692db57b7e6c13899621ac0JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly9pbmR5Y2hvaXIub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25abc72ea47d80c9903d6995d7ba7ce27d8002fb68955f96ecbf6c138e5178e4JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly93d3cuYXZvbmNob2lycy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fd77e7df92dc0e9bd0041533aee281d2498522f3f4a3a7194389498082ed6afJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly93d3cuYXZvbmNob2lyZHJhbWEuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=037f855f1188892db36a00e7c1b9745ba53fd094661d88516f82ea6e7ded4e12JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0Nob2lyXyhtdXNpYyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8135d9e66432360cb6468da6aede0e7cfec65e258ce662e7bffbf8d8aee2b11fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1912413a-7aa4-6524-3ece-56d87b9b64ae&amp;u=a1aHR0cHM6Ly93d3cucm9ja2V0Z2FtZXMuaW8vZ2FtZS9jaG9pcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89af3f649b2a25f7a2392b2c10b56dee33064c88498d4f2f4ebc7dabb5483c3cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb4987440cd81f37d0ec8c57ddd4b73b4433f6f704ef64e6824636472379d340JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95d637c169276316ecd172f1fcab705e49b869f51e338fda629b1d5e8c12ab99JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47e4e0647b232ab1ccea00f3aeaca69c0cc315e9d4d540f7dd3276633f804416JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a29c6d2260a9a6b1ac66744c55524f6d949d31559122af679d6750911c65a96JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ebba92d3b9bc43960970c5cba5015f5026895d35d8a4d10f150bbbcec1d5a5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d5d1a47aefd895efff502a9169dec06f22841d97da28f84df9ccf62a08515d3JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41e45a24674eeff64f530de09951fb2e260aaa86aa08f98d3a2c0a6544a48852JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly9kZWNpZGVyLmNvbS8yMDI2LzA5LzIwL3lvdXRoLXNoYXJvbi1ob3JnYW4taGJvLXJldmlldy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78fc0e82ee49242f61f6b7a63c8390dedc477a23a870a3f9ef8869b71a8e86e8JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjkzMTk2L3lvdXRoLXNlYXNvbi0yLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7af6c63f4ff02708eeee58da9d7f62b6eba09f6e7dde44f69aea0b999c3b9cceJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3107c70d-f84d-660d-018a-d0eff9d7671b&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c20880c3c2f6c4152ebfeaf79d2cfeeb1fac025f5404afb1cc5652b5b2f0447JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnQuZG8v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7a1e8b2b8e31c9346e8c50ca3e61b78d40bad62fffc6930c71eb731e08a0dc5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQzI5NS1Ed190RE50WlhGZUFQQVc2QXc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7f0a044e806a07c8f7f8ce585dccce763cef16777522e5205df0dc71ac907eaJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bFdJMUNIS1RmRjA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be9b8623d9dadf851f24382814b08a7b5b12c0113b905df0c4109a1bc631aca1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DcmFmdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5cc24eae7eadeb89c910a2a057f1ca4183fc70cc8cf9054eef0fc49df7d6fa5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnQuZG8vZG93bmxvYWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce4577f021e36b9b6cc3af15d2304de515e4296fd0f71f57707b7dacea4a6b3eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cuZ29vZGhvdXNla2VlcGluZy5jb20vdHJhdmVsL2hvYmJpZXMtYW5kLWFjdGl2aXRpZXMvZzMyMzM2MTUxL2FkdWx0LWNyYWZ0LWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6aa4dcb8e32d0a71121c5c8ccd09605e92919124b81001160fad47dc68b2c679JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NyYWZ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=58b1a08a94fc72c1790e662d2e7c0eaca64c6641b9ac05154b1b4ac246582fc8JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cuY3JhZnRzcG9ydHN3ZWFyLmNvbS9nbG9iYWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ba162abf38743bfc8e6405cf7e3a9201302f845b15cacd623efe9265ee84650JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cudGhlc3BydWNlY3JhZnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fec06f00f523698654ea951e762cb03db09901ef4dda6f63bb0b64f8ba072d5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36587185-669f-650e-0a35-666767576466&amp;u=a1aHR0cHM6Ly93d3cubWluZWNyYWZ0Lm5ldC9lbi11cy9kb3dubG9hZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77b5103c29099d7c2290887e62757fc6d498d569b613f7bdfcd9036f18672d35JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9leHBlcmllbmNlL3N0b3JhZ2UtZmlsZW1hbmFnZW1lbnQvZGlzay1tYW5hZ2VtZW50LWluLXdpbmRvd3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95efc289cdf7083f4365f7402bf23eab2eed2b4c4f96b968cd2efebb151a9891JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly93d3cuaG93dG9nZWVrLmNvbS83ODcyMTMvNS13YXlzLXRvLW9wZW4tZGlzay1tYW5hZ2VtZW50LW9uLXdpbmRvd3MtMTAtb3ItMTEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8146c40c6ca53a32b71090dff202a925785e9c4d86b82ec1fce728816ea71b5dJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly9sZWFybi5taWNyb3NvZnQuY29tL2VuLXVzL3dpbmRvd3Mtc2VydmVyL3N0b3JhZ2UvZGlzay1tYW5hZ2VtZW50L292ZXJ2aWV3LW9mLWRpc2stbWFuYWdlbWVudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecccf80ba27219b50cd23f9715fed2c112243efa576ea4895ec418e7ab911521JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly93d3cubGlmZXdpcmUuY29tL2hvdy10by1vcGVuLWRpc2stbWFuYWdlbWVudC0yNjI2MDgw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=000b46bf0fd4033daef5ee18ed9691aadd3bc805cece331ca7115266d3b54efeJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly93d3cuZ2Vla3NkaWdpdC5jb20vb3Blbi1kaXNrLW1hbmFnZW1lbnQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04499cd18840c7535dea8c4632ac2f65d3ce060a9b40c14ac768cb62b58aad51JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly93d3cucGFydGl0aW9ud2l6YXJkLmNvbS9wYXJ0aXRpb25tYWdpYy93aW5kb3dzLWRpc2stbWFuYWdlbWVudC1mdWxsLWd1aWRlLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bfa7352c94446fcdd699ef55d4421ceb05be8747a919e88d359889d80b244e9JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vT3Blbi1EaXNjLU1hbmFnZW1lbnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ef78732b753637dccf4826917e473dc9d4a706b5575f59c14dec338496edf61JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly9yZWtvYnl0ZS5jb20vd2luZG93cy9vcGVuLWRpc2stbWFuYWdlbWVudC13aW5kb3dzLTEwLTExLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfa503b271c5ea23b6ae078c9e352dabac9ca11f05059ca403d2ba9c3f7da353JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly9hbGx0aGluZ3MuaG93L2hvdy10by1vcGVuLWRpc2stbWFuYWdlbWVudC1pbi13aW5kb3dzLTExLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1593f7eda36115b301c823374a7b54bc50b5d1f8f623576018af99904d0ca9c4JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2abebbff-bf76-6931-0f11-ac1dbeab682c&amp;u=a1aHR0cHM6Ly9sZWFybi5taWNyb3NvZnQuY29tL2VuLXVzL3dpbmRvd3Mtc2VydmVyL3N0b3JhZ2UvZGlzay1tYW5hZ2VtZW50L21hbmFnZS1kaXNrcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f081beaa692e83c36b7c6b4765aa967ad5b68054c1d2d08be9398bc323d6b392JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9iZW5lZml0c3VzYS5vcmcvZW4vYmxvZy9kaXNhYmlsaXR5LWJlbmVmaXRzLXdoaWxlLXdvcmtpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14bb67dff8a7cf0caff691f28ff17db53f6301f1d07fa8db94be75c5f3618efaJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9kaXNhYmlsaXR5ZXhjaGFuZ2Uub3JnL2Jsb2cvc29jaWFsLXNlY3VyaXR5LWRpc2FiaWxpdHktaW5jb21lLWxpbWl0cy0yMDI2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0164067234b959ee77b2521fb6209b92e002dd36ac7e284029099e0dfb815da2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9zb2NpYWxzZWN1cml0eWRpc2FiaWxpdHkuY29tL3NzZGktZWFybmluZ3MtbGltaXQtMjAyNi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2bb15222cc1fff4e882e0c91db91b79fe5dbf86377ac73ee10bca2649d4d90JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9iZW5lZml0c3VzYS5vcmcvZW4vYmxvZy9zc2RpLWluY29tZS1saW1pdHMtMjAyNi1tYXJyaWVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=777999f2c5d483a9007ba206c4fcae9831806615856e41db38e05164b6944354JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly93d3cuYmVuZWZvcmEub3JnL2FydGljbGVzL3NzZGktcGFydC10aW1lLXdvcms&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=58c6b7f54b0447cb5ed012c925ca2a0af05026c7815038f76d2f8ad23b437639JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly93d3cuam9uYXRoYW5wZW5hLmNvbS91bmRlcnN0YW5kaW5nLXRoZS0yMDI2LXRyaWFsLXdvcmstcGVyaW9kLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63f77a435889724c60a458687b28dcfe964ef2bc146d2220b670378c2a9e52bdJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9hYm91dHNzZGkuY29tL3dvcmtpbmctd2hpbGUtb24tc3NkaS9pbmNvbWUtbGltaXRzLXNnYS9zc2RpLWVhcm5pbmdzLWxpbWl0LTIwMjY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9989b09956bb0097898619007983414e4c4d387a97becb26e3a411a71c0358d1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9nbG9iYWxiZW5lZml0cy5vcmcvMjAyNi8wMy8yMC9zc2RpLWluY29tZS1saW1pdHMtMjAyNi1ob3ctZWFybmluZ3MtYWZmZWN0LXlvdXItYmVuZWZpdHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87c87bfe39183b9870fd648ec14e2839936fb4630a5646d37d3c283ccccaae6eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly93d3cuYnJ1Y2V3ZWlkZXIuY29tL2hvdy1tdWNoLWNhbi1pLWVhcm4tYW5kLXN0aWxsLWdldC1zc2RpLWluLTIwMjYv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fcc623f4bfa4d7127ca41eeb0cf7b8182653b14bd5975ac8deef1aac922c78aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e52508b-c438-6455-3746-4769c5c16564&amp;u=a1aHR0cHM6Ly9zZXR0bGVtZW50aW5zaWdodC5jb20vc29jaWFsLXNlY3VyaXR5LWRpc2FiaWxpdHktYmVuZWZpdHMtcGF5LWNoYXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=879824fd119951307a1df15afa8138da6f4e1f5e662d05d4929996209325ae15JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly81c29zLmNvbS9wYWdlcy90b3Vy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5cd252d17648a1d671a1afe9cb1854d97dd13b09a10e78809fe94a0bae175cdJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly93d3cubGl2ZW5hdGlvbi5jb20vYXJ0aXN0L0s4dlo5MTc4b1gwLzUtc2Vjb25kcy1vZi1zdW1tZXItZXZlbnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b80bc4e4a6d68d351ffda7940dddd5913051864a3226d6a8af3b1886423404a7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly90b3Vyc2V0bGlzdC5jb20vNS1zZWNvbmRzLW9mLXN1bW1lci10b3VyLTIwMjYtZGF0ZXMtc2V0bGlzdC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5923dff38b7e7c4f58e8c0096733bfa7f48784c11f2ec92de4b9c56d7452abb2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly81c29zLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c90c98213d9e21920a2d8cb733d22e394d83467d2c9e80037cd28e307227ba8cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly9jbGltYXRlcGxlZGdlYXJlbmEuY29tLzUtc2Vjb25kcy1vZi1zdW1tZXItYW5ub3VuY2UtZXZlcnlvbmVzLWEtc3Rhci13b3JsZC10b3VyLWtpY2tpbmctb2ZmLWluLW1hcmNoLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f51ed89c330e60f0a3a3c524fd7d753b5801ecc70a01df22bee2e7a645260d4JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly9jbGltYXRlcGxlZGdlYXJlbmEuY29tL2V2ZW50LzUtc2Vjb25kcy1vZi1zdW1tZXItMjYv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ad76111c8da2a8e880490ff87d7a1b125dd91d8ee825b0655ea806cdfe91fabJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2ZiLWFuc3dlcnMvNXNvcy10b3VyLWRhdGVzLWFuZC1sb2NhdGlvbnMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b73eea1616c3bb44969c53a852f3ed6862983c310d2be30853a377be88bd91b7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS81LXNlY29uZHMtb2Ytc3VtbWVyLXRpY2tldHMvYXJ0aXN0LzE3NzgxMTg_bXNvY2tpZD0zOWFhZDk0MjJhZTA2NjFkMzA5NWNlYTAyYjA5NjdhYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dd70fb0ab71e051d2faf95320c812ccf5b8e6b0e2562753dbbe3d982528b9fbJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly93d3cudGlja2V0bWFzdGVyLmNvbS9zZWFyY2g_cT01c29zKyZtc29ja2lkPTM5YWFkOTQyMmFlMDY2MWQzMDk1Y2VhMDJiMDk2N2Fh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c908386246676e1c0b33f0533a8a1af2bac3df5af4aa5594ab0290c05557db57JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39aad942-2ae0-661d-3095-cea02b0967aa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRXZlcnlvbmUlMjdzX2FfU3RhciFfV29ybGRfVG91cg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c76d062456946b50514d7ef991f907f5e59f24e239ac9ba823c51b7406a4e5afJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65961536af690b731a9d14162983486b3adb0a8e2d8972052e75333aa4bd64ceJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tL3RvcGljL3Jldmlld3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c0763d593ad39cdaa3e9eccd91ea22c0d30308942318db3bb9bff026e1a2eb1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDgvMDEvdGhlLWZwdi1kcm9uZS1mb290YWdlLWZyb20tdWtyYWluZS1pcy11bnByZWNlZGVudGVkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7b63736b887c485d617ab1abf3b17537f448426d11b080ce57b316dec8e4e1bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDcvMDkvc29ueS1yeDEwLXYtcmV2aWV3LXNvbWV0aW1lcy10aGUtYmVzdC1zdGlsbC1pc250LWdvb2QtZW5vdWdoLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f2967cf8c8efa45b87815321fbae65de1ae15bc41e5868a0eec29f675e587f1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDQvMDkvY2FpcmEtY2FtZXJhLXJldmlldy1hLXJlYWwtaGVhZC1zY3JhdGNoZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba278da481330846e62f6258c4074be9bd226035fa7f4bcb3988b163a035823bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tL3RvcGljL25ld3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f785ade8fb91c2acbdafa4a761352b4b0b9cc4855597a1e24e9f12733b49c37JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDkvMDgvdGhlLWN1cnJlbnQtY2hhcHRlci1vZi1wZW50YXgtZHNscnMtaXMtb2ZmaWNpYWxseS1vdmVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1649a5b67e331b97d54323a1f5a2bc734fb8fdf07ccb4709c2f474d89b203e69JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDYvMzAvdGhlLTI5LWZpbmFsaXN0cy1mb3ItYXN0cm9ub215LXBob3RvZ3JhcGhlci1vZi10aGUteWVhci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4a64ed7db5f0e55eb83ca0bad550c3d53e8a568bcd559b6d2c61ff118f9e5e0JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDkvMDgvb20tc3lzdGVtLXBlbi1yZXZpZXctdG9vLWZhbWlsaWFyLWJ1dC1vaC1zby1wcmV0dHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1998e9c0875a5975db17b36df5f7401eb64f7a1662b5668bc24acf5c7b95933bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24e4fdd0-7093-6207-1d94-ea3271d86337&amp;u=a1aHR0cHM6Ly9wZXRhcGl4ZWwuY29tLzIwMjYvMDgvMTcvdGlja2V0cy1mb3ItZnVqaWZpbG1zLW5ldy15b3JrLWZ1amlraW5hLWV2ZW50LWNvc3QtMTAtYW5kLWFyZS1vbi1zYWxlLW5vdy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ca54cd8738b4748cad06973d5dd164a30eb536a34a9e31163db6950298d4bd5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ffaf836-6fac-6b6c-1f58-efd46ec06a2e&amp;u=a1aHR0cHM6Ly93d3cubG9rYXlvZ2FzdHVkaW8uY29tLw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -1105,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1139,19 +1169,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1159,19 +1189,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1179,19 +1209,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H4" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1199,19 +1229,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1219,19 +1249,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1239,19 +1269,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H7" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1259,19 +1289,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H8" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1279,19 +1309,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H9" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1299,19 +1329,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G10" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1319,19 +1349,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H11" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1339,19 +1369,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H12" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1359,19 +1389,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G13" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H13" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1379,19 +1409,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H14" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1399,19 +1429,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H15" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1419,19 +1449,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H16" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1439,19 +1469,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G17" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H17" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1459,19 +1489,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G18" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H18" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1479,19 +1509,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G19" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H19" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1499,19 +1529,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G20" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1519,19 +1549,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G21" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H21" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1539,19 +1569,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G22" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H22" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1559,19 +1589,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G23" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H23" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1579,19 +1609,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G24" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H24" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1599,19 +1629,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H25" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1619,19 +1649,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H26" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1639,19 +1669,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G27" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H27" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1659,19 +1689,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G28" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H28" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1679,19 +1709,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G29" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H29" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1699,19 +1729,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G30" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H30" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1719,19 +1749,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G31" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H31" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1739,19 +1769,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G32" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H32" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1759,19 +1789,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G33" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H33" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1779,19 +1809,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G34" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H34" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1799,19 +1829,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G35" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H35" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1819,19 +1849,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G36" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H36" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1839,19 +1869,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G37" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H37" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1859,19 +1889,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G38" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H38" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1879,19 +1909,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G39" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H39" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1899,19 +1929,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G40" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H40" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1919,19 +1949,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G41" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H41" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1939,19 +1969,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G42" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H42" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1959,19 +1989,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G43" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H43" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1979,19 +2009,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G44" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H44" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1999,19 +2029,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G45" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H45" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2019,19 +2049,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H46" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2039,19 +2069,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G47" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H47" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2059,19 +2089,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G48" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H48" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2079,19 +2109,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G49" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H49" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2099,19 +2129,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G50" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H50" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2119,19 +2149,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G51" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H51" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2139,19 +2169,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G52" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2159,19 +2189,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G53" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H53" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2179,19 +2209,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G54" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H54" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2199,19 +2229,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G55" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H55" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2219,19 +2249,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G56" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H56" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2239,19 +2269,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G57" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H57" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2259,19 +2289,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G58" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H58" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2279,19 +2309,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G59" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H59" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2299,19 +2329,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G60" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H60" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2319,19 +2349,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G61" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H61" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2339,19 +2369,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G62" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H62" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2359,19 +2389,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G63" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H63" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2379,19 +2409,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G64" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H64" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2399,19 +2429,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G65" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H65" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2419,19 +2449,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G66" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H66" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2439,19 +2469,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G67" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H67" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2459,19 +2489,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G68" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H68" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2479,19 +2509,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G69" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H69" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2499,19 +2529,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G70" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H70" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2519,19 +2549,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G71" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H71" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2539,19 +2569,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G72" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H72" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2559,19 +2589,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G73" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H73" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2579,19 +2609,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G74" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H74" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2599,19 +2629,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G75" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H75" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2619,19 +2649,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G76" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H76" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2639,19 +2669,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G77" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H77" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2659,19 +2689,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G78" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H78" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2679,19 +2709,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G79" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H79" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2699,19 +2729,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G80" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H80" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2719,19 +2749,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G81" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H81" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2739,19 +2769,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G82" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H82" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2759,19 +2789,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G83" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H83" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2779,19 +2809,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G84" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H84" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2799,19 +2829,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G85" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H85" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2819,19 +2849,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G86" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H86" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2839,19 +2869,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G87" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H87" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2859,19 +2889,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G88" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H88" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2879,19 +2909,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G89" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H89" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2899,19 +2929,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G90" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H90" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2919,19 +2949,19 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G91" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H91" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2939,19 +2969,19 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G92" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H92" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2959,19 +2989,19 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G93" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H93" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2979,19 +3009,19 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G94" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H94" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2999,19 +3029,19 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G95" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H95" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3019,19 +3049,19 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G96" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H96" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3039,19 +3069,19 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H97" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3059,19 +3089,19 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G98" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H98" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3079,19 +3109,19 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G99" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H99" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3099,19 +3129,19 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G100" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H100" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3119,19 +3149,19 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G101" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H101" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3139,19 +3169,19 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G102" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H102" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3159,19 +3189,19 @@
         <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G103" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H103" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3179,19 +3209,19 @@
         <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G104" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H104" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3199,19 +3229,19 @@
         <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G105" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H105" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3219,19 +3249,19 @@
         <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G106" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H106" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3239,19 +3269,19 @@
         <v>113</v>
       </c>
       <c r="B107" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G107" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H107" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3259,19 +3289,19 @@
         <v>114</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G108" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H108" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3279,19 +3309,19 @@
         <v>115</v>
       </c>
       <c r="B109" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C109" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G109" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H109" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3299,19 +3329,19 @@
         <v>116</v>
       </c>
       <c r="B110" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G110" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H110" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3319,19 +3349,19 @@
         <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G111" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H111" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3339,19 +3369,19 @@
         <v>118</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C112" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G112" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="H112" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3359,19 +3389,19 @@
         <v>119</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C113" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G113" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H113" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3379,19 +3409,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G114" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H114" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3399,19 +3429,19 @@
         <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C115" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G115" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H115" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3419,19 +3449,19 @@
         <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G116" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H116" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3439,19 +3469,119 @@
         <v>123</v>
       </c>
       <c r="B117" t="s">
+        <v>129</v>
+      </c>
+      <c r="C117" t="s">
+        <v>130</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G117" t="s">
+        <v>256</v>
+      </c>
+      <c r="H117" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
         <v>124</v>
       </c>
-      <c r="C117" t="s">
+      <c r="B118" t="s">
+        <v>129</v>
+      </c>
+      <c r="C118" t="s">
+        <v>130</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G118" t="s">
+        <v>256</v>
+      </c>
+      <c r="H118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
         <v>125</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G117" t="s">
-        <v>247</v>
-      </c>
-      <c r="H117" t="s">
+      <c r="B119" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" t="s">
+        <v>130</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>248</v>
+      </c>
+      <c r="G119" t="s">
+        <v>256</v>
+      </c>
+      <c r="H119" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>129</v>
+      </c>
+      <c r="C120" t="s">
+        <v>130</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G120" t="s">
+        <v>256</v>
+      </c>
+      <c r="H120" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>129</v>
+      </c>
+      <c r="C121" t="s">
+        <v>130</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G121" t="s">
+        <v>256</v>
+      </c>
+      <c r="H121" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C122" t="s">
+        <v>130</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G122" t="s">
+        <v>257</v>
+      </c>
+      <c r="H122" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3572,6 +3702,11 @@
     <hyperlink ref="F115" r:id="rId114"/>
     <hyperlink ref="F116" r:id="rId115"/>
     <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
